--- a/res/OffersProvider.xlsx
+++ b/res/OffersProvider.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Eclipse\workspace-sts-3.7.3.RELEASE\WordPropertiesGenerator\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Github\msword-properties-generator\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3A7F94-2E79-4148-9860-41563A6F5D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2053191-4F2B-473C-AA4B-C2AAC9C1934D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33132" yWindow="636" windowWidth="23388" windowHeight="7476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45972" yWindow="-108" windowWidth="34776" windowHeight="21096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="new" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
